--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a2fed59b41ca10b7/Documents/UiPath/Desafio_One4Tech/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bento\Downloads\uipath-desafio-main\uipath-desafio-main\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{00D541BD-CB78-4D75-8532-9AD73E8C785E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FCABD4E9-01B4-4BF2-8502-1A4B160F3271}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD6A1F57-7045-4F17-859F-CA3C0E487FFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4740" yWindow="4200" windowWidth="19425" windowHeight="11025" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="54">
   <si>
     <t>Name</t>
   </si>
@@ -175,6 +175,18 @@
   </si>
   <si>
     <t>Data\Output\</t>
+  </si>
+  <si>
+    <t>ArquivoInput</t>
+  </si>
+  <si>
+    <t>PastaInput</t>
+  </si>
+  <si>
+    <t>Insumo_RPA_One4Tech.xlsx</t>
+  </si>
+  <si>
+    <t>Data\Input\</t>
   </si>
 </sst>
 </file>
@@ -251,10 +263,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -645,8 +653,22 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="14.25" customHeight="1"/>
-    <row r="9" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="8" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" ht="14.25" customHeight="1">
+      <c r="A9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" t="s">
+        <v>52</v>
+      </c>
+    </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="11" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="12" spans="1:26" ht="14.25" customHeight="1"/>
